--- a/data/trans_orig/P57B3_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>45677</t>
+          <t>51978</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34569</t>
+          <t>38630</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62292</t>
+          <t>66653</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37609</t>
+          <t>44996</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>33645</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47077</t>
+          <t>57315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>83286</t>
+          <t>96974</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68804</t>
+          <t>78281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101437</t>
+          <t>116195</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>458510</t>
+          <t>497486</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441895</t>
+          <t>482811</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>469618</t>
+          <t>510834</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>409858</t>
+          <t>443415</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>400390</t>
+          <t>431096</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>419410</t>
+          <t>454766</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>868368</t>
+          <t>940901</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>850217</t>
+          <t>921680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>882850</t>
+          <t>959594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504187</t>
+          <t>549464</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504187</t>
+          <t>549464</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504187</t>
+          <t>549464</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951654</t>
+          <t>1037875</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951654</t>
+          <t>1037875</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951654</t>
+          <t>1037875</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,102 +1068,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38521</t>
+          <t>42860</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28220</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50260</t>
+          <t>55711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>11,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>42414</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>32687</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>53127</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>85274</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>69735</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>100464</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>11,11%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>36999</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>28789</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>47614</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>75520</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>61505</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>90483</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -1181,102 +1181,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>413692</t>
+          <t>440352</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401953</t>
+          <t>427501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423993</t>
+          <t>450862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>88,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>378963</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>368250</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>388690</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>89,93%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>87,39%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>819315</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>804125</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>834854</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>88,89%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>343909</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>333294</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>352119</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,29%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>87,5%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>92,44%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>757601</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>742638</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>771616</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>90,94%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>89,14%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>380908</t>
+          <t>421377</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>380908</t>
+          <t>421377</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380908</t>
+          <t>421377</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833121</t>
+          <t>904589</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833121</t>
+          <t>904589</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833121</t>
+          <t>904589</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>294924</t>
+          <t>55241</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71448</t>
+          <t>43002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>519960</t>
+          <t>70620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>28420</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>35952</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>321021</t>
+          <t>83661</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102070</t>
+          <t>68704</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>594460</t>
+          <t>100654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>373340</t>
+          <t>416371</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148304</t>
+          <t>400992</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>596816</t>
+          <t>428610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>140815</t>
+          <t>159077</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133279</t>
+          <t>151545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147456</t>
+          <t>166373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>514154</t>
+          <t>575448</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240715</t>
+          <t>558455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>733105</t>
+          <t>590405</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>132017</t>
+          <t>147648</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112694</t>
+          <t>126209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153520</t>
+          <t>171693</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73642</t>
+          <t>83711</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40162</t>
+          <t>69444</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101762</t>
+          <t>100429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>205659</t>
+          <t>231360</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138706</t>
+          <t>205036</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>238485</t>
+          <t>257895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>901934</t>
+          <t>983267</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>880431</t>
+          <t>959222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>921257</t>
+          <t>1004706</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>904452</t>
+          <t>777500</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>876332</t>
+          <t>760782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>937932</t>
+          <t>791767</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1806386</t>
+          <t>1760767</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1773560</t>
+          <t>1734232</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1873339</t>
+          <t>1787091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033951</t>
+          <t>1130915</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033951</t>
+          <t>1130915</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033951</t>
+          <t>1130915</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012045</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012045</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012045</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>83519</t>
+          <t>103116</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69189</t>
+          <t>84877</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100878</t>
+          <t>121735</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>139315</t>
+          <t>163344</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104112</t>
+          <t>144383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161650</t>
+          <t>182390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>222834</t>
+          <t>266461</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>186068</t>
+          <t>239544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>253517</t>
+          <t>295904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>391527</t>
+          <t>464848</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>374168</t>
+          <t>446229</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>405857</t>
+          <t>483087</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>700484</t>
+          <t>665841</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>678149</t>
+          <t>646795</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>735687</t>
+          <t>684802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1092011</t>
+          <t>1130688</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1061328</t>
+          <t>1101245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1128777</t>
+          <t>1157605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>82,85%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>839799</t>
+          <t>829185</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>839799</t>
+          <t>829185</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>839799</t>
+          <t>829185</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314845</t>
+          <t>1397149</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314845</t>
+          <t>1397149</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314845</t>
+          <t>1397149</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>22108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>116917</t>
+          <t>130865</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>101193</t>
+          <t>113828</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133886</t>
+          <t>149765</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>126052</t>
+          <t>141081</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109275</t>
+          <t>120587</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148719</t>
+          <t>161946</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>231372</t>
+          <t>227012</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217748</t>
+          <t>215120</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236217</t>
+          <t>232256</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>642221</t>
+          <t>711047</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>625252</t>
+          <t>692147</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>657945</t>
+          <t>728084</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>873593</t>
+          <t>938058</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>850926</t>
+          <t>917193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>890370</t>
+          <t>958552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759138</t>
+          <t>841912</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759138</t>
+          <t>841912</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759138</t>
+          <t>841912</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>999645</t>
+          <t>1079139</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>999645</t>
+          <t>1079139</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>999645</t>
+          <t>1079139</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>603793</t>
+          <t>411059</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>374956</t>
+          <t>377646</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1372590</t>
+          <t>451872</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>430578</t>
+          <t>493750</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>343304</t>
+          <t>459497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>473143</t>
+          <t>528018</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1034371</t>
+          <t>904809</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>788780</t>
+          <t>858404</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1774533</t>
+          <t>957747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2770374</t>
+          <t>3029335</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2001577</t>
+          <t>2988522</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2999211</t>
+          <t>3062748</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3141738</t>
+          <t>3135843</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3099173</t>
+          <t>3101575</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3229012</t>
+          <t>3170096</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5912112</t>
+          <t>6165178</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5171950</t>
+          <t>6112240</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6157703</t>
+          <t>6211583</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>87,86%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374167</t>
+          <t>3440394</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374167</t>
+          <t>3440394</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374167</t>
+          <t>3440394</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3572316</t>
+          <t>3629593</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3572316</t>
+          <t>3629593</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3572316</t>
+          <t>3629593</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6946483</t>
+          <t>7069987</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6946483</t>
+          <t>7069987</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6946483</t>
+          <t>7069987</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
